--- a/result/持仓天数分析.xlsx
+++ b/result/持仓天数分析.xlsx
@@ -485,10 +485,10 @@
         <v>337</v>
       </c>
       <c r="C2" t="n">
-        <v>31.43323442136499</v>
+        <v>31.51928783382789</v>
       </c>
       <c r="D2" t="n">
-        <v>52.72267820348146</v>
+        <v>52.8939900219646</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>

--- a/result/持仓天数分析.xlsx
+++ b/result/持仓天数分析.xlsx
@@ -516,25 +516,25 @@
         <v>235</v>
       </c>
       <c r="C3" t="n">
-        <v>6.306382978723405</v>
+        <v>13.29787234042553</v>
       </c>
       <c r="D3" t="n">
-        <v>6.038317966933715</v>
+        <v>12.41331462861969</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/result/持仓天数分析.xlsx
+++ b/result/持仓天数分析.xlsx
@@ -485,10 +485,10 @@
         <v>337</v>
       </c>
       <c r="C2" t="n">
-        <v>31.51928783382789</v>
+        <v>31.6053412462908</v>
       </c>
       <c r="D2" t="n">
-        <v>52.8939900219646</v>
+        <v>53.06623529636371</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>

--- a/result/持仓天数分析.xlsx
+++ b/result/持仓天数分析.xlsx
@@ -482,13 +482,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C2" t="n">
-        <v>31.6053412462908</v>
+        <v>30.74715909090909</v>
       </c>
       <c r="D2" t="n">
-        <v>53.06623529636371</v>
+        <v>52.51412771949906</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -500,7 +500,7 @@
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I2" t="n">
         <v>255</v>
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C3" t="n">
-        <v>13.29787234042553</v>
+        <v>13.19166666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>12.41331462861969</v>
+        <v>12.35377795844587</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>

--- a/result/持仓天数分析.xlsx
+++ b/result/持仓天数分析.xlsx
@@ -482,13 +482,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="C2" t="n">
-        <v>30.74715909090909</v>
+        <v>29.46052631578947</v>
       </c>
       <c r="D2" t="n">
-        <v>52.51412771949906</v>
+        <v>51.56383977441583</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -500,7 +500,7 @@
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>27.25</v>
       </c>
       <c r="I2" t="n">
         <v>255</v>
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C3" t="n">
-        <v>13.19166666666667</v>
+        <v>13.16935483870968</v>
       </c>
       <c r="D3" t="n">
-        <v>12.35377795844587</v>
+        <v>12.20653689225244</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
